--- a/e2e/expectedData/Non_Regular_Cutah_Semester_1.xlsx
+++ b/e2e/expectedData/Non_Regular_Cutah_Semester_1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -77,24 +77,27 @@
     <t>IV</t>
   </si>
   <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>0,50</t>
+  </si>
+  <si>
+    <t>85,00</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
     <t>Expat</t>
   </si>
   <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>0,50</t>
-  </si>
-  <si>
-    <t>85,00</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
     <t>0,25</t>
   </si>
   <si>
@@ -146,6 +149,9 @@
     <t>CLAUDIO DA COSTA ALVES</t>
   </si>
   <si>
+    <t>Outsource</t>
+  </si>
+  <si>
     <t>52,50</t>
   </si>
   <si>
@@ -164,7 +170,7 @@
     <t>1.186,00</t>
   </si>
   <si>
-    <t>DILI, 26 August 2026</t>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -751,7 +757,7 @@
         <v>25</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>21</v>
@@ -760,25 +766,25 @@
         <v>21</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>21</v>
@@ -789,13 +795,13 @@
         <v>79001</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>21</v>
@@ -822,7 +828,7 @@
         <v>22</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>21</v>
@@ -833,13 +839,13 @@
         <v>91009</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>21</v>
@@ -866,7 +872,7 @@
         <v>22</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>21</v>
@@ -877,40 +883,40 @@
         <v>74003</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>21</v>
@@ -921,14 +927,14 @@
         <v>91015</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="E12" s="3" t="s">
         <v>21</v>
       </c>
@@ -954,7 +960,7 @@
         <v>22</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>21</v>
@@ -965,13 +971,13 @@
         <v>26013</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>21</v>
@@ -998,7 +1004,7 @@
         <v>22</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>21</v>
@@ -1009,13 +1015,13 @@
         <v>95008</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>21</v>
@@ -1024,25 +1030,25 @@
         <v>21</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>21</v>
@@ -1053,13 +1059,13 @@
         <v>24005</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>21</v>
@@ -1086,7 +1092,7 @@
         <v>22</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>21</v>
@@ -1097,13 +1103,13 @@
         <v>999999</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>21</v>
@@ -1130,7 +1136,7 @@
         <v>22</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>21</v>
@@ -1138,7 +1144,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1152,7 +1158,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N17" s="4" t="s">
         <v>21</v>
@@ -1163,13 +1169,13 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H19"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1178,7 +1184,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
@@ -1189,11 +1195,11 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F21"/>
       <c r="J21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:14" customHeight="1" ht="37.5">
@@ -1203,20 +1209,20 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F23"/>
       <c r="J23" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F24"/>
       <c r="J24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/e2e/expectedData/Non_Regular_Cutah_Semester_1.xlsx
+++ b/e2e/expectedData/Non_Regular_Cutah_Semester_1.xlsx
@@ -95,21 +95,24 @@
     <t>VI</t>
   </si>
   <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>22,50</t>
+  </si>
+  <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
     <t>Expat</t>
   </si>
   <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>22,50</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>III</t>
-  </si>
-  <si>
     <t>75,00</t>
   </si>
   <si>
@@ -149,9 +152,6 @@
     <t>CLAUDIO DA COSTA ALVES</t>
   </si>
   <si>
-    <t>Outsource</t>
-  </si>
-  <si>
     <t>52,50</t>
   </si>
   <si>
@@ -170,7 +170,7 @@
     <t>1.186,00</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -801,7 +801,7 @@
         <v>30</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>21</v>
@@ -828,7 +828,7 @@
         <v>22</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>21</v>
@@ -839,13 +839,13 @@
         <v>91009</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>21</v>
@@ -872,7 +872,7 @@
         <v>22</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>21</v>
@@ -883,40 +883,40 @@
         <v>74003</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>21</v>
@@ -927,13 +927,13 @@
         <v>91015</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>21</v>
@@ -960,7 +960,7 @@
         <v>22</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>21</v>
@@ -971,13 +971,13 @@
         <v>26013</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>21</v>
@@ -1004,7 +1004,7 @@
         <v>22</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>21</v>
@@ -1015,13 +1015,13 @@
         <v>95008</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>21</v>
@@ -1030,25 +1030,25 @@
         <v>21</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>21</v>
@@ -1059,13 +1059,13 @@
         <v>24005</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>21</v>
@@ -1109,7 +1109,7 @@
         <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>21</v>
